--- a/argano/docs/lista-verifica-normativa.xlsx
+++ b/argano/docs/lista-verifica-normativa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$95</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Voci'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -722,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3513,27 +3513,27 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Vano: ingombri tipici</t>
+          <t>Vano: porte</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Ingombri tipici nel vano (modificabili su ogni progetto)</t>
+          <t>Vano porta di piano e operatore della porta di cabina</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>profondità della porta di piano 80 mm; gioco tra le soglie 30 mm; porta di cabina 80 mm; pareti della cabina 35 mm; guide e staffe della cabina 165 mm per lato; cabina–contrappeso 60 mm; spessore del contrappeso 140 mm; guide e staffe del contrappeso 80 mm; cabina–parete di fondo 60 mm</t>
+          <t>vano nel muro: luce netta + 2 × 50 mm di portale; operatore della porta di cabina lungo 2·L + 60 mm e profondo 150 mm; con due accessi adiacenti gli operatori non devono sovrapporsi all'angolo tra le porte (altrimenti «Attenzione»: operatori da scegliere con il fornitore)</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>dati del costruttore di guide, porte e cabina</t>
+          <t>dato del fornitore delle porte</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>valori tipici: scelta del software</t>
+          <t>valori tipici: scelta del software da confermare con il fornitore</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>la cabina entra nel vano</t>
+          <t>ingombro della seconda porta di piano; operatori delle porte adiacenti</t>
         </is>
       </c>
       <c r="I60" s="11" t="n"/>
@@ -3553,7 +3553,7 @@
       <c r="M60" s="11" t="n"/>
       <c r="N60" s="11" t="n"/>
     </row>
-    <row r="61" ht="95" customHeight="1">
+    <row r="61" ht="108" customHeight="1">
       <c r="A61" s="10" t="n">
         <v>59</v>
       </c>
@@ -3564,32 +3564,32 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Contrappeso laterale</t>
+          <t>Ingombri tipici nel vano (modificabili su ogni progetto)</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>la guida della cabina su quel lato sta a metà profondità della cabina, il contrappeso dietro di essa, a 100 mm dal suo asse e a 40 mm dalla parete di fondo; lunghezza del contrappeso in pianta da 400 a 900 mm (sotto 400 mm: «Attenzione»); con il contrappeso sul fondo, al massimo la larghezza tra le guide della cabina</t>
+          <t>profondità della porta di piano 80 mm; gioco tra le soglie 30 mm; porta di cabina 80 mm; pareti della cabina 35 mm; guide e staffe della cabina 165 mm per lato; cabina–contrappeso 60 mm; spessore del contrappeso 140 mm; guide e staffe del contrappeso 80 mm; cabina–parete di fondo 60 mm; punta della guida–cabina 30 mm; contrappeso laterale–piede della guida di cabina 85 mm</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>dati del costruttore di guide, porte e cabina</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
+          <t>valori tipici: scelta del software</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
           <t>scelta del software</t>
         </is>
       </c>
-      <c r="G61" s="10" t="inlineStr">
-        <is>
-          <t>scelta del software</t>
-        </is>
-      </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>lunghezza del contrappeso</t>
+          <t>la cabina entra nel vano</t>
         </is>
       </c>
       <c r="I61" s="11" t="n"/>
@@ -3599,23 +3599,23 @@
       <c r="M61" s="11" t="n"/>
       <c r="N61" s="11" t="n"/>
     </row>
-    <row r="62" ht="43" customHeight="1">
+    <row r="62" ht="108" customHeight="1">
       <c r="A62" s="10" t="n">
         <v>60</v>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Dimensioni proposte della cabina</t>
+          <t>Contrappeso laterale</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
+          <t>tra la parete e la guida della cabina, centrato sull'asse delle guide di cabina, con le sue guide alle estremità (pattini 20 mm) e la guida di cabina su una staffa a ponte; a 40 mm dalle zone delle porte; lunghezza in pianta da 400 a 900 mm (sotto 400 mm: «Attenzione»); con il contrappeso sul fondo, al massimo la larghezza tra le guide della cabina</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>lunghezza del contrappeso</t>
         </is>
       </c>
       <c r="I62" s="11" t="n"/>
@@ -3645,33 +3645,33 @@
       <c r="M62" s="11" t="n"/>
       <c r="N62" s="11" t="n"/>
     </row>
-    <row r="63" ht="43" customHeight="1">
+    <row r="63" ht="108" customHeight="1">
       <c r="A63" s="10" t="n">
         <v>61</v>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Vano: limiti del progetto</t>
+          <t>Vano: ingombri tipici</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Limiti del progetto in pianta</t>
+          <t>Arcata a zaino (due accessi adiacenti a 90°)</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>solo la pianta: fossa, testata e spazi di rifugio non sono verificati; il rilievo dal disegno CAD va controllato in cantiere</t>
+          <t>entrambe le guide di cabina sulla parete opposta all'accesso laterale, con le lame affacciate lungo la parete (il momento della cabina a sbalzo va sulle facce delle lame); piedi delle guide a 20 mm dentro la profondità della piattaforma; contrappeso tra le guide, contro la parete, con le sue guide alle estremità e i piedi a 70 mm da quelli delle guide di cabina (staffe)</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.2.5.7 e 5.2.5.8 (fossa e testata)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>limite del modello attuale</t>
+          <t>scelta del software (principio: cataloghi di arcate a zaino); disposizione da confermare con il fornitore dell'arcata</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
@@ -3691,10 +3691,1482 @@
       <c r="M63" s="11" t="n"/>
       <c r="N63" s="11" t="n"/>
     </row>
+    <row r="64" ht="82" customHeight="1">
+      <c r="A64" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>Spazi di rifugio sul tetto di cabina e in fossa</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>tipo 1 (in piedi) 400 × 500 mm in pianta, alto 2000 mm; tipo 2 (accucciato) 500 × 700 mm, alto 1000 mm; tipo 3 (disteso, solo in fossa) 700 × 1000 mm, alto 500 mm; in testata con la cabina nella posizione più alta, in fossa con la cabina sugli ammortizzatori compressi</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-20:2020, 5.2.5.7.1 e 5.2.5.8.1 (Tabella 3)</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>spazio di rifugio in testata; spazio di rifugio in fossa</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="n"/>
+      <c r="J64" s="11" t="n"/>
+      <c r="K64" s="11" t="n"/>
+      <c r="L64" s="11" t="n"/>
+      <c r="M64" s="11" t="n"/>
+      <c r="N64" s="11" t="n"/>
+    </row>
+    <row r="65" ht="56" customHeight="1">
+      <c r="A65" s="10" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>Posizione più alta della cabina</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>contrappeso sugli ammortizzatori completamente compressi, più il salto 0,035·v² m (v velocità nominale)</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-20:2020, 5.2.5.6.1 (Tabella 2)</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>spazio di rifugio in testata; distanze libere dal soffitto</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="11" t="n"/>
+      <c r="K65" s="11" t="n"/>
+      <c r="L65" s="11" t="n"/>
+      <c r="M65" s="11" t="n"/>
+      <c r="N65" s="11" t="n"/>
+    </row>
+    <row r="66" ht="56" customHeight="1">
+      <c r="A66" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Distanze libere dal soffitto con la cabina nella posizione più alta</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>≥ 500 mm sopra le apparecchiature sul tetto di cabina (operatore); ≥ 100 mm sopra pattini, attacchi delle funi e traversa dell'arcata; ≥ 300 mm sopra il corrimano della balaustra</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-20:2020, 5.2.5.7.2</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>distanze libere dal soffitto</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="11" t="n"/>
+      <c r="K66" s="11" t="n"/>
+      <c r="L66" s="11" t="n"/>
+      <c r="M66" s="11" t="n"/>
+      <c r="N66" s="11" t="n"/>
+    </row>
+    <row r="67" ht="56" customHeight="1">
+      <c r="A67" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Distanze in fossa con la cabina sugli ammortizzatori compressi</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>≥ 500 mm dal pavimento della fossa alle parti più basse della cabina; grembiule alto ≥ 750 mm sotto la soglia di cabina, con ≥ 100 mm liberi dal pavimento della fossa</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-20:2020, 5.2.5.8.2 e 5.4.5</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>spazio di rifugio in fossa; grembiule sugli ammortizzatori compressi</t>
+        </is>
+      </c>
+      <c r="I67" s="11" t="n"/>
+      <c r="J67" s="11" t="n"/>
+      <c r="K67" s="11" t="n"/>
+      <c r="L67" s="11" t="n"/>
+      <c r="M67" s="11" t="n"/>
+      <c r="N67" s="11" t="n"/>
+    </row>
+    <row r="68" ht="56" customHeight="1">
+      <c r="A68" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Balaustra sul tetto di cabina</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>richiesta se la distanza libera dal tetto alla parete supera 300 mm: alta 700 mm fino a 500 mm di distanza, 1100 mm oltre</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-20:2020, 5.4.7.4</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>balaustra sul tetto di cabina</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="n"/>
+      <c r="J68" s="11" t="n"/>
+      <c r="K68" s="11" t="n"/>
+      <c r="L68" s="11" t="n"/>
+      <c r="M68" s="11" t="n"/>
+      <c r="N68" s="11" t="n"/>
+    </row>
+    <row r="69" ht="56" customHeight="1">
+      <c r="A69" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Superficie dove una persona può stare sul tetto di cabina</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>area continua ≥ 0,12 m² con il lato minore ≥ 250 mm (disegnata 400 × 300 mm); sopra di essa deve esserci l'altezza dello spazio di rifugio</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-20:2020, 5.2.5.7.3</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="n"/>
+      <c r="J69" s="11" t="n"/>
+      <c r="K69" s="11" t="n"/>
+      <c r="L69" s="11" t="n"/>
+      <c r="M69" s="11" t="n"/>
+      <c r="N69" s="11" t="n"/>
+    </row>
+    <row r="70" ht="56" customHeight="1">
+      <c r="A70" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>Schermo del contrappeso in fossa</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>dal punto più basso del contrappeso sugli ammortizzatori compressi fino ad almeno 2000 mm sopra il pavimento della fossa</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-20:2020, 5.2.5.5.1</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="n"/>
+      <c r="J70" s="11" t="n"/>
+      <c r="K70" s="11" t="n"/>
+      <c r="L70" s="11" t="n"/>
+      <c r="M70" s="11" t="n"/>
+      <c r="N70" s="11" t="n"/>
+    </row>
+    <row r="71" ht="56" customHeight="1">
+      <c r="A71" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>Vano: sezione, spazi di rifugio e ammortizzatori</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>Ammortizzatori ad accumulo di energia lineari (molle)</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>ammessi fino a 1 m/s; corsa ≥ 0,135·v² m e comunque ≥ 65 mm; extracorsa della cabina e del contrappeso ≥ 0 (nessun minimo nella norma)</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-20:2020, 5.8.2.2</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>corsa degli ammortizzatori di cabina; corsa dell'ammortizzatore del contrappeso; extracorsa di cabina e contrappeso</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="n"/>
+      <c r="J71" s="11" t="n"/>
+      <c r="K71" s="11" t="n"/>
+      <c r="L71" s="11" t="n"/>
+      <c r="M71" s="11" t="n"/>
+      <c r="N71" s="11" t="n"/>
+    </row>
+    <row r="72" ht="69" customHeight="1">
+      <c r="A72" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>Locale del macchinario</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Locale del macchinario</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>altezza libera delle zone di lavoro ≥ 2100 mm (1800 mm sui percorsi); davanti al quadro una superficie libera profonda ≥ 700 mm e larga ≥ 500 mm o quanto il quadro; porta di accesso ≥ 600 × 2000 mm</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-20:2020, 5.2.6.3.2.1 e 5.2.3</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>altezza del locale macchina; superficie libera davanti al quadro; porta del locale macchina</t>
+        </is>
+      </c>
+      <c r="I72" s="11" t="n"/>
+      <c r="J72" s="11" t="n"/>
+      <c r="K72" s="11" t="n"/>
+      <c r="L72" s="11" t="n"/>
+      <c r="M72" s="11" t="n"/>
+      <c r="N72" s="11" t="n"/>
+    </row>
+    <row r="73" ht="69" customHeight="1">
+      <c r="A73" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>Locale del macchinario</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>Illuminazione del vano e del locale del macchinario</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>vano: illuminazione fissa di almeno 50 lux a 1 m sopra il tetto della cabina e sopra il pavimento della fossa, 20 lux altrove; locale del macchinario: almeno 200 lux al pavimento nelle zone di lavoro</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-20:2020, 5.2.1.4</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="n"/>
+      <c r="J73" s="11" t="n"/>
+      <c r="K73" s="11" t="n"/>
+      <c r="L73" s="11" t="n"/>
+      <c r="M73" s="11" t="n"/>
+      <c r="N73" s="11" t="n"/>
+    </row>
+    <row r="74" ht="56" customHeight="1">
+      <c r="A74" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>Locale del macchinario</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>Temperatura dei locali del macchinario e degli armadi</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>temperatura ambiente mantenuta tra +5 °C e +40 °C: ipotesi della norma, da garantire nell'edificio</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-20:2020, introduzione (ipotesi)</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="n"/>
+      <c r="J74" s="11" t="n"/>
+      <c r="K74" s="11" t="n"/>
+      <c r="L74" s="11" t="n"/>
+      <c r="M74" s="11" t="n"/>
+      <c r="N74" s="11" t="n"/>
+    </row>
+    <row r="75" ht="108" customHeight="1">
+      <c r="A75" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Carichi sul pavimento della fossa</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>sotto ogni ammortizzatore 4 volte il carico statico: 4·g·(P+Q) per la cabina, 4·g·M_cw per il contrappeso, divisi tra gli ammortizzatori; sotto ogni guida di cabina la massa della guida più la reazione all'intervento del paracadute k1·g·(P+Q)/2 (k1 = 2 progressivo, 3 istantaneo a rulli, 5 istantaneo); sotto ogni guida del contrappeso la massa della guida</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-20:2020, 5.2.1.8; UNI EN 81-50:2020, 5.10</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>sintesi della UNI EN 81-20:2020 di costruttori e organismi notificati (KONE, Sodimas, MCCAA), fonti secondarie concordi; sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="n"/>
+      <c r="J75" s="11" t="n"/>
+      <c r="K75" s="11" t="n"/>
+      <c r="L75" s="11" t="n"/>
+      <c r="M75" s="11" t="n"/>
+      <c r="N75" s="11" t="n"/>
+    </row>
+    <row r="76" ht="108" customHeight="1">
+      <c r="A76" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>Spinte sulle guide di cabina</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>portata spostata di 1/8 della cabina dal centro, più lo scostamento della cabina dalle guide (arcata a zaino); intervento del paracadute: Fx = k1·g·(Q·xQ + P·xP)/(n·h) sulle facce delle lame, Fy = k1·g·(Q·yQ + P·yP)/((n/2)·h) sulle punte; marcia: k2 = 1,2; n = 2 guide, h = distanza tra i pattini, presa pari all'ingombro verticale dell'arcata; si riporta il caso più gravoso</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-50:2020, 5.10</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>sintesi della UNI EN 81-50:2020 (Elevator World, GMV, tesi UC3M), fonti secondarie</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="n"/>
+      <c r="J76" s="11" t="n"/>
+      <c r="K76" s="11" t="n"/>
+      <c r="L76" s="11" t="n"/>
+      <c r="M76" s="11" t="n"/>
+      <c r="N76" s="11" t="n"/>
+    </row>
+    <row r="77" ht="82" customHeight="1">
+      <c r="A77" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>Carico della macchina sulla soletta</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>carico statico sull'asse (cabina, portata, contrappeso, funi, cavi; in taglia 2:1 la metà di cabina, portata e contrappeso) × 1,5 come coefficiente dinamico, modificabile nei dati dell'impianto; sulla soletta anche la massa di macchina e telaio</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>prassi di progetto: la EN 81 non fissa un coefficiente dinamico per gli appoggi della macchina (in altre prassi 2,0)</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="inlineStr">
+        <is>
+          <t>prassi di cantiere</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="n"/>
+      <c r="J77" s="11" t="n"/>
+      <c r="K77" s="11" t="n"/>
+      <c r="L77" s="11" t="n"/>
+      <c r="M77" s="11" t="n"/>
+      <c r="N77" s="11" t="n"/>
+    </row>
+    <row r="78" ht="43" customHeight="1">
+      <c r="A78" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>Massa dei cavi flessibili</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>0,5 kg/m per metà della corsa più 3 m, se non data nei dati dell'impianto (cavo piatto 24G0,75)</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>schede dei costruttori di cavi piatti (0,48–0,57 kg/m)</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>stima</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="n"/>
+      <c r="J78" s="11" t="n"/>
+      <c r="K78" s="11" t="n"/>
+      <c r="L78" s="11" t="n"/>
+      <c r="M78" s="11" t="n"/>
+      <c r="N78" s="11" t="n"/>
+    </row>
+    <row r="79" ht="82" customHeight="1">
+      <c r="A79" s="10" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>Carichi sull'edificio e spinte sulle guide</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>Lunghezze stimate nel foglio dei dati</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>guide dal pavimento della fossa fino a 50 mm sotto la soletta del vano; fune del limitatore: due volte l'altezza dalla fossa al limitatore, posto 800 mm sopra il pavimento del locale; funi di trazione: taglia × (corsa + 2 × tratto oltre la corsa), più deviazione o rinvii</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>stima del software, da sostituire con le misure di cantiere</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>stima</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="n"/>
+      <c r="J79" s="11" t="n"/>
+      <c r="K79" s="11" t="n"/>
+      <c r="L79" s="11" t="n"/>
+      <c r="M79" s="11" t="n"/>
+      <c r="N79" s="11" t="n"/>
+    </row>
+    <row r="80" ht="43" customHeight="1">
+      <c r="A80" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>Vano: limiti del progetto</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>Dimensioni proposte della cabina</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>la cabina più grande che entra nel vano, a passi di 10 mm, con superficie entro il limite della portata; a parità di superficie, la più profonda</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="11" t="n"/>
+      <c r="J80" s="11" t="n"/>
+      <c r="K80" s="11" t="n"/>
+      <c r="L80" s="11" t="n"/>
+      <c r="M80" s="11" t="n"/>
+      <c r="N80" s="11" t="n"/>
+    </row>
+    <row r="81" ht="82" customHeight="1">
+      <c r="A81" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>Vano: limiti del progetto</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>Limiti del modello del vano</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>limite del modello attuale</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="n"/>
+      <c r="J81" s="11" t="n"/>
+      <c r="K81" s="11" t="n"/>
+      <c r="L81" s="11" t="n"/>
+      <c r="M81" s="11" t="n"/>
+      <c r="N81" s="11" t="n"/>
+    </row>
+    <row r="82" ht="56" customHeight="1">
+      <c r="A82" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Corsa</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>dati dei piani inseriti</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>derivazione</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="11" t="n"/>
+      <c r="J82" s="11" t="n"/>
+      <c r="K82" s="11" t="n"/>
+      <c r="L82" s="11" t="n"/>
+      <c r="M82" s="11" t="n"/>
+      <c r="N82" s="11" t="n"/>
+    </row>
+    <row r="83" ht="56" customHeight="1">
+      <c r="A83" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>Portata e velocità</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-20:2020, 5.4.2.1</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>progetto del vano</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>derivazione</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="n"/>
+      <c r="J83" s="11" t="n"/>
+      <c r="K83" s="11" t="n"/>
+      <c r="L83" s="11" t="n"/>
+      <c r="M83" s="11" t="n"/>
+      <c r="N83" s="11" t="n"/>
+    </row>
+    <row r="84" ht="69" customHeight="1">
+      <c r="A84" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software, senza fonte</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>stima</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="n"/>
+      <c r="J84" s="11" t="n"/>
+      <c r="K84" s="11" t="n"/>
+      <c r="L84" s="11" t="n"/>
+      <c r="M84" s="11" t="n"/>
+      <c r="N84" s="11" t="n"/>
+    </row>
+    <row r="85" ht="82" customHeight="1">
+      <c r="A85" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>Fune oltre la corsa (L0)</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale (macchina in basso o senza locale: fino al soffitto del vano)</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="n"/>
+      <c r="J85" s="11" t="n"/>
+      <c r="K85" s="11" t="n"/>
+      <c r="L85" s="11" t="n"/>
+      <c r="M85" s="11" t="n"/>
+      <c r="N85" s="11" t="n"/>
+    </row>
+    <row r="86" ht="56" customHeight="1">
+      <c r="A86" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2: la puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, capitolo 5.3</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>pianta del vano</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>derivazione</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I86" s="11" t="n"/>
+      <c r="J86" s="11" t="n"/>
+      <c r="K86" s="11" t="n"/>
+      <c r="L86" s="11" t="n"/>
+      <c r="M86" s="11" t="n"/>
+      <c r="N86" s="11" t="n"/>
+    </row>
+    <row r="87" ht="56" customHeight="1">
+      <c r="A87" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>corsa + testata: la macchina al livello del piano più basso, le pulegge sotto il soffitto del vano</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, capitolo 5</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>dati verticali del vano</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>derivazione</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="n"/>
+      <c r="J87" s="11" t="n"/>
+      <c r="K87" s="11" t="n"/>
+      <c r="L87" s="11" t="n"/>
+      <c r="M87" s="11" t="n"/>
+      <c r="N87" s="11" t="n"/>
+    </row>
+    <row r="88" ht="56" customHeight="1">
+      <c r="A88" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>ricerca, capitolo 8</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>motore di calcolo</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" s="11" t="n"/>
+      <c r="J88" s="11" t="n"/>
+      <c r="K88" s="11" t="n"/>
+      <c r="L88" s="11" t="n"/>
+      <c r="M88" s="11" t="n"/>
+      <c r="N88" s="11" t="n"/>
+    </row>
+    <row r="89" ht="69" customHeight="1">
+      <c r="A89" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>motore di calcolo (src/calc/model.ts)</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>derivazione</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="n"/>
+      <c r="J89" s="11" t="n"/>
+      <c r="K89" s="11" t="n"/>
+      <c r="L89" s="11" t="n"/>
+      <c r="M89" s="11" t="n"/>
+      <c r="N89" s="11" t="n"/>
+    </row>
+    <row r="90" ht="56" customHeight="1">
+      <c r="A90" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
+        </is>
+      </c>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I90" s="11" t="n"/>
+      <c r="J90" s="11" t="n"/>
+      <c r="K90" s="11" t="n"/>
+      <c r="L90" s="11" t="n"/>
+      <c r="M90" s="11" t="n"/>
+      <c r="N90" s="11" t="n"/>
+    </row>
+    <row r="91" ht="69" customHeight="1">
+      <c r="A91" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>Limite di aderenza mostrato durante la marcia</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-50:2020, 5.11.2.2</t>
+        </is>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="n"/>
+      <c r="J91" s="11" t="n"/>
+      <c r="K91" s="11" t="n"/>
+      <c r="L91" s="11" t="n"/>
+      <c r="M91" s="11" t="n"/>
+      <c r="N91" s="11" t="n"/>
+    </row>
+    <row r="92" ht="43" customHeight="1">
+      <c r="A92" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>Tempi delle porte</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software (solo animazione)</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H92" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="n"/>
+      <c r="J92" s="11" t="n"/>
+      <c r="K92" s="11" t="n"/>
+      <c r="L92" s="11" t="n"/>
+      <c r="M92" s="11" t="n"/>
+      <c r="N92" s="11" t="n"/>
+    </row>
+    <row r="93" ht="69" customHeight="1">
+      <c r="A93" s="10" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa; la verifica della corsa resta quella della sezione</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>velocità d'urto 1,15 volte la nominale; ammortizzatore lineare con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa); la cabina e il contrappeso si separano all'urto</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-20:2020, 5.8.2.2</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>da verificare</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="n"/>
+      <c r="J93" s="11" t="n"/>
+      <c r="K93" s="11" t="n"/>
+      <c r="L93" s="11" t="n"/>
+      <c r="M93" s="11" t="n"/>
+      <c r="N93" s="11" t="n"/>
+    </row>
+    <row r="94" ht="56" customHeight="1">
+      <c r="A94" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>Cabina bloccata: rotazione in salita</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>UNI EN 81-50:2020, 5.11.2</t>
+        </is>
+      </c>
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>motore di calcolo; velocità scelta dal software</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="n"/>
+      <c r="J94" s="11" t="n"/>
+      <c r="K94" s="11" t="n"/>
+      <c r="L94" s="11" t="n"/>
+      <c r="M94" s="11" t="n"/>
+      <c r="N94" s="11" t="n"/>
+    </row>
+    <row r="95" ht="43" customHeight="1">
+      <c r="A95" s="10" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>Passo di campionamento</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H95" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="n"/>
+      <c r="J95" s="11" t="n"/>
+      <c r="K95" s="11" t="n"/>
+      <c r="L95" s="11" t="n"/>
+      <c r="M95" s="11" t="n"/>
+      <c r="N95" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N63"/>
+  <autoFilter ref="A1:N95"/>
   <dataValidations count="1">
-    <dataValidation sqref="I3:I63" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
+    <dataValidation sqref="I3:I95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
       <formula1>"conforme,diverso,non applicabile"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3737,7 +5209,7 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$63,"da verificare")</f>
+        <f>COUNTIF(Voci!$G$3:$G$95,"da verificare")</f>
         <v/>
       </c>
     </row>
@@ -3748,7 +5220,7 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$63,"confermato")</f>
+        <f>COUNTIF(Voci!$G$3:$G$95,"confermato")</f>
         <v/>
       </c>
     </row>
@@ -3759,7 +5231,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$63,"scelta del software")</f>
+        <f>COUNTIF(Voci!$G$3:$G$95,"scelta del software")</f>
         <v/>
       </c>
     </row>
@@ -3770,7 +5242,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$63,"stima")</f>
+        <f>COUNTIF(Voci!$G$3:$G$95,"stima")</f>
         <v/>
       </c>
     </row>
@@ -3781,7 +5253,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$63,"derivazione")</f>
+        <f>COUNTIF(Voci!$G$3:$G$95,"derivazione")</f>
         <v/>
       </c>
     </row>
@@ -3792,7 +5264,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$63,"prassi di cantiere")</f>
+        <f>COUNTIF(Voci!$G$3:$G$95,"prassi di cantiere")</f>
         <v/>
       </c>
     </row>
@@ -3803,7 +5275,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTA(Voci!$A$3:$A$63)</f>
+        <f>COUNTA(Voci!$A$3:$A$95)</f>
         <v/>
       </c>
     </row>
@@ -3821,7 +5293,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$63,"conforme")</f>
+        <f>COUNTIF(Voci!$I$3:$I$95,"conforme")</f>
         <v/>
       </c>
     </row>
@@ -3832,7 +5304,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$63,"diverso")</f>
+        <f>COUNTIF(Voci!$I$3:$I$95,"diverso")</f>
         <v/>
       </c>
     </row>
@@ -3843,7 +5315,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$63,"non applicabile")</f>
+        <f>COUNTIF(Voci!$I$3:$I$95,"non applicabile")</f>
         <v/>
       </c>
     </row>
@@ -3854,14 +5326,14 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>COUNTBLANK(Voci!$I$3:$I$63)</f>
+        <f>COUNTBLANK(Voci!$I$3:$I$95)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Conteggi sulle righe 3–63 del foglio «Voci» (la riga 2 è l'esempio).</t>
+          <t>Conteggi sulle righe 3–95 del foglio «Voci» (la riga 2 è l'esempio).</t>
         </is>
       </c>
     </row>

--- a/argano/docs/lista-verifica-normativa.xlsx
+++ b/argano/docs/lista-verifica-normativa.xlsx
@@ -4703,7 +4703,7 @@
       <c r="M85" s="11" t="n"/>
       <c r="N85" s="11" t="n"/>
     </row>
-    <row r="86" ht="56" customHeight="1">
+    <row r="86" ht="108" customHeight="1">
       <c r="A86" s="10" t="n">
         <v>84</v>
       </c>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2: la puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso</t>
+          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (con taglia 2:1 anche − Dp: le funi salgono dal lato interno delle pulegge di cabina e di contrappeso): la puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso, rinvio semplice; se le pulegge non entrano così, la distanza va misurata sull'impianto</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">

--- a/argano/docs/lista-verifica-normativa.xlsx
+++ b/argano/docs/lista-verifica-normativa.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Voci'!$A$1:$N$96</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Voci'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -722,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N95"/>
+  <dimension ref="A1:N96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3507,7 +3507,7 @@
       <c r="M59" s="11" t="n"/>
       <c r="N59" s="11" t="n"/>
     </row>
-    <row r="60" ht="82" customHeight="1">
+    <row r="60" ht="108" customHeight="1">
       <c r="A60" s="10" t="n">
         <v>58</v>
       </c>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>vano nel muro: luce netta + 2 × 50 mm di portale; operatore della porta di cabina lungo 2·L + 60 mm e profondo 150 mm; con due accessi adiacenti gli operatori non devono sovrapporsi all'angolo tra le porte (altrimenti «Attenzione»: operatori da scegliere con il fornitore)</t>
+          <t>vano nel muro: luce netta + 2 × 50 mm di portale; operatore della porta di cabina lungo 1,5·L + 50 mm con porta telescopica (il lato di chiusura 25 mm oltre la luce) e 2·L + 60 mm con porta centrale, profondo 150 mm, dentro il vano; con due accessi adiacenti gli operatori non devono sovrapporsi all'angolo tra le porte (altrimenti «Attenzione»: operatori da scegliere con il fornitore)</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
@@ -3533,17 +3533,17 @@
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>valori tipici: scelta del software da confermare con il fornitore</t>
+          <t>cataloghi 2SG FLY 2AT (1,5·A + 40) e 2AO (2·A + 20), Fermator 40/10 VF (1,5·PL + 40/50; 2·PL + 50; chiusura a 25 mm dalla luce), letti da estratti di ricerca: presi i valori più lunghi, da confermare con il fornitore</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>ingombro della seconda porta di piano; operatori delle porte adiacenti</t>
+          <t>ingombro della porta di piano; ingombro della seconda porta di piano; operatori delle porte adiacenti</t>
         </is>
       </c>
       <c r="I60" s="11" t="n"/>
@@ -3645,7 +3645,7 @@
       <c r="M62" s="11" t="n"/>
       <c r="N62" s="11" t="n"/>
     </row>
-    <row r="63" ht="108" customHeight="1">
+    <row r="63" ht="147" customHeight="1">
       <c r="A63" s="10" t="n">
         <v>61</v>
       </c>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>entrambe le guide di cabina sulla parete opposta all'accesso laterale, con le lame affacciate lungo la parete (il momento della cabina a sbalzo va sulle facce delle lame); piedi delle guide a 20 mm dentro la profondità della piattaforma; contrappeso tra le guide, contro la parete, con le sue guide alle estremità e i piedi a 70 mm da quelli delle guide di cabina (staffe)</t>
+          <t>entrambe le guide di cabina sulla parete opposta all'accesso laterale, con le lame affacciate lungo la parete (il momento della cabina a sbalzo va sulle facce delle lame); piedi delle guide a 20 mm dentro la profondità della piattaforma; contrappeso tra le guide, contro la parete, con le sue guide alle estremità e i piedi a 70 mm da quelli delle guide di cabina (staffe); la cabina a 10 mm dalle bride che tengono i piedi delle guide sulle staffe (bride forgiate della misura della guida, con la piastra oltre il piede)</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
@@ -4473,7 +4473,7 @@
       <c r="M80" s="11" t="n"/>
       <c r="N80" s="11" t="n"/>
     </row>
-    <row r="81" ht="82" customHeight="1">
+    <row r="81" ht="134" customHeight="1">
       <c r="A81" s="10" t="n">
         <v>79</v>
       </c>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Limiti del modello del vano</t>
+          <t>Quote della pianta fissate a mano</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
+          <t>ogni quota della pianta (cabina, porte, operatore della porta di cabina, guide, contrappeso) si può fissare a mano al posto di quella proposta; la cabina resta fuori dalle zone di porte, guide e contrappeso, le guide del contrappeso nel loro spazio (laterale: fuori dalle zone delle porte che ha di fronte più il gioco d'estremità; arcata a zaino: tra i piedi delle guide di cabina meno il gioco delle staffe) e la luce di ogni porta dentro la cabina; altrimenti «Non conforme»</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>limite del modello attuale</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>quote fissate a mano: ingombri al loro posto; quote fissate a mano: porte dentro la cabina</t>
         </is>
       </c>
       <c r="I81" s="11" t="n"/>
@@ -4519,23 +4519,23 @@
       <c r="M81" s="11" t="n"/>
       <c r="N81" s="11" t="n"/>
     </row>
-    <row r="82" ht="56" customHeight="1">
+    <row r="82" ht="82" customHeight="1">
       <c r="A82" s="10" t="n">
         <v>80</v>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
+          <t>Vano: limiti del progetto</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Corsa</t>
+          <t>Limiti del modello del vano</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
+          <t>pianta, sezione A-A e locale macchina da un modello semplificato: arcata, operatori delle porte, ammortizzatori e macchina hanno posizioni e ingombri tipici, da sostituire con i dati dei fornitori; il rilievo dal disegno CAD va controllato in cantiere</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>dati dei piani inseriti</t>
+          <t>limite del modello attuale</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
@@ -4576,22 +4576,22 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Portata e velocità</t>
+          <t>Corsa</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
+          <t>somma delle altezze tra i piani, dal più basso al più alto</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.4.2.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>progetto del vano</t>
+          <t>dati dei piani inseriti</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
@@ -4611,7 +4611,7 @@
       <c r="M83" s="11" t="n"/>
       <c r="N83" s="11" t="n"/>
     </row>
-    <row r="84" ht="69" customHeight="1">
+    <row r="84" ht="56" customHeight="1">
       <c r="A84" s="10" t="n">
         <v>82</v>
       </c>
@@ -4622,27 +4622,27 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
+          <t>Portata e velocità</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
+          <t>la portata inserita, oppure quella della cabina più grande che entra nel vano (Tabella 6); la velocità è una sola per il vano e per la macchina</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
+          <t>UNI EN 81-20:2020, 5.4.2.1</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>scelta del software, senza fonte</t>
+          <t>progetto del vano</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>stima</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
@@ -4657,7 +4657,7 @@
       <c r="M84" s="11" t="n"/>
       <c r="N84" s="11" t="n"/>
     </row>
-    <row r="85" ht="82" customHeight="1">
+    <row r="85" ht="69" customHeight="1">
       <c r="A85" s="10" t="n">
         <v>83</v>
       </c>
@@ -4668,27 +4668,27 @@
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Fune oltre la corsa (L0)</t>
+          <t>Massa della cabina non inserita — va sostituita con la massa del libretto o con quella ricavata dalla prova di bilanciamento; la sensibilità ±10% ne mostra l'effetto</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale (macchina in basso o senza locale: fino al soffitto del vano)</t>
+          <t>P = 1,1·Q arrotondata per eccesso a 10 kg: valore di partenza per far girare il calcolo</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ricerca, capitoli 3 e 6 (origine della massa della cabina)</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
+          <t>scelta del software, senza fonte</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>stima</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
@@ -4703,7 +4703,7 @@
       <c r="M85" s="11" t="n"/>
       <c r="N85" s="11" t="n"/>
     </row>
-    <row r="86" ht="108" customHeight="1">
+    <row r="86" ht="82" customHeight="1">
       <c r="A86" s="10" t="n">
         <v>84</v>
       </c>
@@ -4714,27 +4714,27 @@
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
+          <t>Fune oltre la corsa (L0)</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (con taglia 2:1 anche − Dp: le funi salgono dal lato interno delle pulegge di cabina e di contrappeso): la puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso, rinvio semplice; se le pulegge non entrano così, la distanza va misurata sull'impianto</t>
+          <t>dalla sommità dell'arcata con la cabina all'ultimo piano fino all'asse della puleggia: testata − sommità dell'arcata + solaio del locale + asse della puleggia a 0,9·D sul pavimento del locale (macchina in basso o senza locale: fino al soffitto del vano)</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>pianta del vano</t>
+          <t>dati verticali del vano; altezza dell'asse scelta dal software</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
@@ -4749,7 +4749,7 @@
       <c r="M86" s="11" t="n"/>
       <c r="N86" s="11" t="n"/>
     </row>
-    <row r="87" ht="56" customHeight="1">
+    <row r="87" ht="147" customHeight="1">
       <c r="A87" s="10" t="n">
         <v>85</v>
       </c>
@@ -4760,22 +4760,22 @@
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
+          <t>Distanza orizzontale della puleggia di rinvio (dx)</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>corsa + testata: la macchina al livello del piano più basso, le pulegge sotto il soffitto del vano</t>
+          <t>calata tra la fune di cabina e quella del contrappeso in pianta − D/2 − Dp/2 (rinvio semplice: la fune scende dal lato esterno della puleggia di rinvio); se la fune deve rientrare, − D/2 + Dp/2 (rinvio inverso: dal lato interno); con taglia 2:1 la calata è minore di Dp, perché le funi salgono dal lato interno delle pulegge di cabina e di contrappeso. La puleggia di trazione sopra la cabina, il rinvio sopra il contrappeso; se nessuna delle due geometrie torna con l'angolo di avvolgimento, la distanza va misurata sull'impianto</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 5</t>
+          <t>ricerca, capitolo 5.3</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>dati verticali del vano</t>
+          <t>pianta del vano</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
@@ -4806,27 +4806,27 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori</t>
+          <t>Macchina in basso: altezza fino alle pulegge in alto (Hv)</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
+          <t>corsa + testata: la macchina al livello del piano più basso, le pulegge sotto il soffitto del vano</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>ricerca, capitolo 8</t>
+          <t>ricerca, capitolo 5</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo</t>
+          <t>dati verticali del vano</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
@@ -4841,38 +4841,38 @@
       <c r="M88" s="11" t="n"/>
       <c r="N88" s="11" t="n"/>
     </row>
-    <row r="89" ht="69" customHeight="1">
+    <row r="89" ht="134" customHeight="1">
       <c r="A89" s="10" t="n">
         <v>87</v>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Simulazione nel tempo (3D e grafici)</t>
+          <t>Impianto: valori calcolati dai dati inseriti una volta</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
+          <t>Macchina proposta — una griglia di calcolo, non un catalogo: il modello reale va scelto dal costruttore con questi valori. La puleggia cambia la geometria delle funi (fune oltre la corsa, distanza del rinvio): ogni puleggia della griglia è dimensionata con la propria, e con il rinvio dalla pianta solo le pulegge per cui la pianta sa posizionare il rinvio</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
+          <t>la prima opzione del dimensionamento (capitolo 8): puleggia, funi, rapporto, gola, motore e freno che passano ogni verifica; con le ipotesi del gruppo (poli, giri, rendimenti, inerzie) inserite</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
+          <t>ricerca, capitolo 8</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo (src/calc/model.ts)</t>
+          <t>motore di calcolo</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>derivazione</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
@@ -4887,7 +4887,7 @@
       <c r="M89" s="11" t="n"/>
       <c r="N89" s="11" t="n"/>
     </row>
-    <row r="90" ht="56" customHeight="1">
+    <row r="90" ht="69" customHeight="1">
       <c r="A90" s="10" t="n">
         <v>88</v>
       </c>
@@ -4898,27 +4898,27 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
+          <t>Forze nella simulazione — agli estremi della corsa e alle accelerazioni della verifica i valori coincidono con quelli della verifica (test automatico)</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
+          <t>tiri delle funi, T1/T2, e^(f·α), coppie e decelerazione del freno con le stesse funzioni della verifica (modello delle funi del motore di calcolo), valutate istante per istante con la posizione e l'accelerazione della cabina</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
+          <t>UNI EN 81-50:2020, 5.11 (aderenza); ricerca, capitolo 4</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>motore di calcolo (src/calc/model.ts)</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>derivazione</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
@@ -4933,7 +4933,7 @@
       <c r="M90" s="11" t="n"/>
       <c r="N90" s="11" t="n"/>
     </row>
-    <row r="91" ht="69" customHeight="1">
+    <row r="91" ht="56" customHeight="1">
       <c r="A91" s="10" t="n">
         <v>89</v>
       </c>
@@ -4944,17 +4944,17 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Limite di aderenza mostrato durante la marcia</t>
+          <t>Profilo del moto tra i piani — accelerazione e strappo sono dati di progetto dell'azionamento, non limiti normativi</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
+          <t>profilo a strappo limitato: velocità nominale, accelerazione di progetto e strappo 1 m/s³; se il tragitto è corto, la velocità più alta che ci sta</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2.2</t>
+          <t>ISO 18738-1:2012 (misura della qualità di marcia, nessun limite)</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
@@ -4979,7 +4979,7 @@
       <c r="M91" s="11" t="n"/>
       <c r="N91" s="11" t="n"/>
     </row>
-    <row r="92" ht="43" customHeight="1">
+    <row r="92" ht="69" customHeight="1">
       <c r="A92" s="10" t="n">
         <v>90</v>
       </c>
@@ -4990,22 +4990,22 @@
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Tempi delle porte</t>
+          <t>Limite di aderenza mostrato durante la marcia</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
+          <t>e^(f·α) con il coefficiente d'attrito della frenatura (μ ridotto con la velocità delle funi): il confronto è indicativo (oltre il limite: avviso, non verifica fallita), la verifica resta quella dei casi della norma</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2.2</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>scelta del software (solo animazione)</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
@@ -5025,7 +5025,7 @@
       <c r="M92" s="11" t="n"/>
       <c r="N92" s="11" t="n"/>
     </row>
-    <row r="93" ht="69" customHeight="1">
+    <row r="93" ht="43" customHeight="1">
       <c r="A93" s="10" t="n">
         <v>91</v>
       </c>
@@ -5036,27 +5036,27 @@
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa; la verifica della corsa resta quella della sezione</t>
+          <t>Tempi delle porte</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>velocità d'urto 1,15 volte la nominale; ammortizzatore lineare con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa); la cabina e il contrappeso si separano all'urto</t>
+          <t>apertura 2,5 s, chiusura 3 s, sosta a porte aperte 3 s, partenza 0,5 s dopo la chiusura</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-20:2020, 5.8.2.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
+          <t>scelta del software (solo animazione)</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>da verificare</t>
+          <t>scelta del software</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
@@ -5071,7 +5071,7 @@
       <c r="M93" s="11" t="n"/>
       <c r="N93" s="11" t="n"/>
     </row>
-    <row r="94" ht="56" customHeight="1">
+    <row r="94" ht="69" customHeight="1">
       <c r="A94" s="10" t="n">
         <v>92</v>
       </c>
@@ -5082,27 +5082,27 @@
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Cabina bloccata: rotazione in salita</t>
+          <t>Urto sugli ammortizzatori — la rigidezza è una scelta del software coerente con i carichi sulla fossa; la verifica della corsa resta quella della sezione</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
+          <t>velocità d'urto 1,15 volte la nominale; ammortizzatore lineare con la corsa piena a 4 volte il carico statico (lo stesso valore dei carichi sulla fossa); la cabina e il contrappeso si separano all'urto</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>UNI EN 81-50:2020, 5.11.2</t>
+          <t>UNI EN 81-20:2020, 5.8.2.2</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>motore di calcolo; velocità scelta dal software</t>
+          <t>sintesi della norma di costruttori e organismi notificati (fonti secondarie)</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>da verificare</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
@@ -5117,7 +5117,7 @@
       <c r="M94" s="11" t="n"/>
       <c r="N94" s="11" t="n"/>
     </row>
-    <row r="95" ht="43" customHeight="1">
+    <row r="95" ht="56" customHeight="1">
       <c r="A95" s="10" t="n">
         <v>93</v>
       </c>
@@ -5128,22 +5128,22 @@
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Passo di campionamento</t>
+          <t>Cabina bloccata: rotazione in salita</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+          <t>la macchina gira in salita a 0,3 m/s finché il contrappeso poggia sui suoi ammortizzatori; poi le funi devono slittare (T1/T2 ≥ e^(f·α), μ della cabina bloccata)</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNI EN 81-50:2020, 5.11.2</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>scelta del software</t>
+          <t>motore di calcolo; velocità scelta dal software</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
@@ -5163,10 +5163,56 @@
       <c r="M95" s="11" t="n"/>
       <c r="N95" s="11" t="n"/>
     </row>
+    <row r="96" ht="43" customHeight="1">
+      <c r="A96" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>Simulazione nel tempo (3D e grafici)</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>Passo di campionamento</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>0,02 s; tra due campioni i valori sono interpolati linearmente</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>scelta del software</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="n"/>
+      <c r="J96" s="11" t="n"/>
+      <c r="K96" s="11" t="n"/>
+      <c r="L96" s="11" t="n"/>
+      <c r="M96" s="11" t="n"/>
+      <c r="N96" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N95"/>
+  <autoFilter ref="A1:N96"/>
   <dataValidations count="1">
-    <dataValidation sqref="I3:I95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
+    <dataValidation sqref="I3:I96" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Esito" error="Scegliere: conforme, diverso, non applicabile." type="list">
       <formula1>"conforme,diverso,non applicabile"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5209,7 +5255,7 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$95,"da verificare")</f>
+        <f>COUNTIF(Voci!$G$3:$G$96,"da verificare")</f>
         <v/>
       </c>
     </row>
@@ -5220,7 +5266,7 @@
         </is>
       </c>
       <c r="B5" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$95,"confermato")</f>
+        <f>COUNTIF(Voci!$G$3:$G$96,"confermato")</f>
         <v/>
       </c>
     </row>
@@ -5231,7 +5277,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$95,"scelta del software")</f>
+        <f>COUNTIF(Voci!$G$3:$G$96,"scelta del software")</f>
         <v/>
       </c>
     </row>
@@ -5242,7 +5288,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$95,"stima")</f>
+        <f>COUNTIF(Voci!$G$3:$G$96,"stima")</f>
         <v/>
       </c>
     </row>
@@ -5253,7 +5299,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$95,"derivazione")</f>
+        <f>COUNTIF(Voci!$G$3:$G$96,"derivazione")</f>
         <v/>
       </c>
     </row>
@@ -5264,7 +5310,7 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIF(Voci!$G$3:$G$95,"prassi di cantiere")</f>
+        <f>COUNTIF(Voci!$G$3:$G$96,"prassi di cantiere")</f>
         <v/>
       </c>
     </row>
@@ -5275,7 +5321,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <f>COUNTA(Voci!$A$3:$A$95)</f>
+        <f>COUNTA(Voci!$A$3:$A$96)</f>
         <v/>
       </c>
     </row>
@@ -5293,7 +5339,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$95,"conforme")</f>
+        <f>COUNTIF(Voci!$I$3:$I$96,"conforme")</f>
         <v/>
       </c>
     </row>
@@ -5304,7 +5350,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$95,"diverso")</f>
+        <f>COUNTIF(Voci!$I$3:$I$96,"diverso")</f>
         <v/>
       </c>
     </row>
@@ -5315,7 +5361,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>COUNTIF(Voci!$I$3:$I$95,"non applicabile")</f>
+        <f>COUNTIF(Voci!$I$3:$I$96,"non applicabile")</f>
         <v/>
       </c>
     </row>
@@ -5326,14 +5372,14 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>COUNTBLANK(Voci!$I$3:$I$95)</f>
+        <f>COUNTBLANK(Voci!$I$3:$I$96)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Conteggi sulle righe 3–95 del foglio «Voci» (la riga 2 è l'esempio).</t>
+          <t>Conteggi sulle righe 3–96 del foglio «Voci» (la riga 2 è l'esempio).</t>
         </is>
       </c>
     </row>
